--- a/Tradeoff.xlsx
+++ b/Tradeoff.xlsx
@@ -991,7 +991,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="es-CO"/>
         </a:p>
@@ -1421,7 +1421,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="es-CO"/>
           </a:p>
@@ -1483,7 +1483,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="es-CO"/>
           </a:p>
@@ -1521,7 +1521,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="es-CO"/>
         </a:p>
@@ -2014,7 +2014,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Capacidad para ser auditado</t>
+          <t>Capacidad de ser auditado</t>
         </is>
       </c>
       <c r="B5" s="6" t="n"/>
@@ -2241,7 +2241,7 @@
     <col width="12.21875" bestFit="1" customWidth="1" min="4" max="4"/>
     <col width="11.77734375" bestFit="1" customWidth="1" min="5" max="5"/>
     <col width="16.21875" bestFit="1" customWidth="1" min="6" max="6"/>
-    <col hidden="1" min="7" max="7"/>
+    <col hidden="1" width="13" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2327,7 +2327,7 @@
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>Capacidad para ser auditado</t>
+          <t>Capacidad de ser auditado</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
@@ -6220,7 +6220,7 @@
     <row r="11" ht="69" customHeight="1">
       <c r="A11" s="137" t="inlineStr">
         <is>
-          <t>Auditabilidad</t>
+          <t>Capacidad de ser auditado</t>
         </is>
       </c>
       <c r="B11" s="91" t="inlineStr">
@@ -6699,21 +6699,32 @@
   <sheetData>
     <row r="1" ht="36.75" customHeight="1">
       <c r="A1" s="57" t="inlineStr"/>
+      <c r="B1" s="142" t="n"/>
       <c r="C1" s="57" t="inlineStr">
         <is>
           <t>Metadata</t>
         </is>
       </c>
+      <c r="D1" s="141" t="n"/>
+      <c r="E1" s="141" t="n"/>
+      <c r="F1" s="142" t="n"/>
       <c r="G1" s="57" t="inlineStr">
         <is>
           <t>Scenario Definition</t>
         </is>
       </c>
+      <c r="H1" s="141" t="n"/>
+      <c r="I1" s="141" t="n"/>
+      <c r="J1" s="141" t="n"/>
+      <c r="K1" s="141" t="n"/>
+      <c r="L1" s="142" t="n"/>
       <c r="M1" s="57" t="inlineStr">
         <is>
           <t>Architecture Notes</t>
         </is>
       </c>
+      <c r="N1" s="141" t="n"/>
+      <c r="O1" s="142" t="n"/>
     </row>
     <row r="2" ht="90" customHeight="1">
       <c r="A2" s="57" t="inlineStr">
